--- a/mario/ops/cvxlab_models/Split_sut/model_settings.xlsx
+++ b/mario/ops/cvxlab_models/Split_sut/model_settings.xlsx
@@ -3371,7 +3371,7 @@
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
-          <t>Minimize(sum(entropy(U_s_p,U0_s_p))+sum(entropy(U_c_n,U0_c_n))+sum(entropy(M_a_pn,M0_a_pn))+sum(entropy(M_pn_s,M0_pn_s))+sum(entropy(V,V0))+sum(entropy(Y,Y0)))</t>
+          <t>Minimize(sum(entropy(U_s_p,U0_s_p))+sum(entropy(U_c_n,U0_c_n))+sum(entropy(M_a_pn,M0_a_pn))+sum(entropy(M_pn_s,M0_pn_s))+sum(entropy_signed(V,V0))+sum(entropy_signed(Y,Y0)))</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3575,7 +3575,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yold&lt;=(I_c_from_to_p@I_com_p_pn@Y_r)*(1+eps)</t>
+          <t>Yold-absval(Yold)*eps&lt;=(I_c_from_to_p@I_com_p_pn@Y_r)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3587,7 +3587,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yold&gt;=(I_c_from_to_p@I_com_p_pn@Y_r)*(1-eps)</t>
+          <t>Yold+absval(Yold)*eps&gt;=(I_c_from_to_p@I_com_p_pn@Y_r)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3599,7 +3599,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vold&lt;=(V_r@I_act_p_pn@I_a_from_to_p)*(1+eps)</t>
+          <t>Vold-absval(Vold)*eps&lt;=(V_r@I_act_p_pn@I_a_from_to_p)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3611,7 +3611,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vold&gt;=(V_r@I_act_p_pn@I_a_from_to_p)*(1-eps)</t>
+          <t>Vold+absval(Vold)*eps&gt;=(V_r@I_act_p_pn@I_a_from_to_p)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
